--- a/corpus/xlsx/level-016/template.xlsx
+++ b/corpus/xlsx/level-016/template.xlsx
@@ -78,89 +78,89 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">{t</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">i</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">tl</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">e</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">}}</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">{{</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">cu</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">st</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">om</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">er</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">}}</t>
+      <t xml:space="preserve">d.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">t</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">it</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">l</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">e}</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">{d</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">.c</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">us</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">to</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">me</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">r}</t>
     </r>
   </si>
   <si>
@@ -178,39 +178,39 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">{c</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">o</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">un</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">t</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">}}</t>
+      <t xml:space="preserve">d.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">c</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">ou</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">n</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">t}</t>
     </r>
   </si>
   <si>
@@ -228,39 +228,39 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">{s</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">pa</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">c</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">ed</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">}}</t>
+      <t xml:space="preserve">d.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">sp</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">a</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">ce</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">d}</t>
     </r>
   </si>
   <si>
@@ -278,39 +278,39 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">{e</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">na</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">bl</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">ed</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">}}</t>
+      <t xml:space="preserve">d.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">en</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">ab</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">le</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">d}</t>
     </r>
   </si>
   <si>
@@ -328,39 +328,39 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">{l</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">it</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">er</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">al</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">}}</t>
+      <t xml:space="preserve">d.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">li</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">te</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">ra</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">l}</t>
     </r>
   </si>
 </sst>
